--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652291</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652350</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652301</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652302</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652315</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652303</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652305</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1677,6 +1722,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652351</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652304</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652349</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,6 +2313,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652352</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,8 +2425,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652354</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134652346</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>134652351</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134652304</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134652306</v>
       </c>
       <c r="B13" t="n">
-        <v>57801</v>
+        <v>57803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134652346</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>134652351</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134652304</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134652306</v>
       </c>
       <c r="B13" t="n">
-        <v>57803</v>
+        <v>57804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134652346</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>134652351</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134652304</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134652306</v>
       </c>
       <c r="B13" t="n">
-        <v>57804</v>
+        <v>57808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134652346</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>134652351</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134652304</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134652306</v>
       </c>
       <c r="B13" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134652303</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>134652305</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>134652346</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>134652351</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>134652304</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>134652306</v>
       </c>
       <c r="B13" t="n">
-        <v>57809</v>
+        <v>57814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27073-2026 artfynd.xlsx
+++ b/artfynd/A 27073-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652347</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652350</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652301</v>
       </c>
       <c r="B5" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>134652302</v>
       </c>
       <c r="B6" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>134652315</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>134652349</v>
       </c>
       <c r="B14" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134652352</v>
       </c>
       <c r="B15" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>134652354</v>
       </c>
       <c r="B16" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
